--- a/artfynd/A 22811-2026 artfynd.xlsx
+++ b/artfynd/A 22811-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>344863</v>
+        <v>95575</v>
       </c>
       <c r="B2" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodknulen, Jmt</t>
+          <t>Övsjöbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546990.846455205</v>
+        <v>546752</v>
       </c>
       <c r="R2" t="n">
-        <v>6987562.93786025</v>
+        <v>6987383</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-10-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-10-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-10-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -806,6 +791,601 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>344841</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Övsjöbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>546708</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6987432</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2009-10-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2009-10-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>344842</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Övsjöbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>546752</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6987383</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-10-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-10-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>344862</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bodknulen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>546906</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6987507</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2009-10-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2009-10-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>344863</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bodknulen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>546991</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6987563</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2009-10-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2009-10-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>359925</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Övsjöbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546819</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6987479</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2009-10-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2009-10-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22811-2026 artfynd.xlsx
+++ b/artfynd/A 22811-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95575</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/344841</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/344842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/344862</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/344863</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,8 +1416,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/359925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>